--- a/data/opendata/testsExport.xlsx
+++ b/data/opendata/testsExport.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,34 @@
         </is>
       </c>
       <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-16 14:22:46.435453</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>58ce0efd3aaa2a713dbc4138eb1329e3</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/opendata/testsExport.xlsx
+++ b/data/opendata/testsExport.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,118 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-16 16:43:44.479683</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>58ce0efd3aaa2a713dbc4138eb1329e3</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-16 17:00:45.411476</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>58ce0efd3aaa2a713dbc4138eb1329e3</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-16 17:01:56.145331</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>58ce0efd3aaa2a713dbc4138eb1329e3</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-16 17:03:07.071900</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>58ce0efd3aaa2a713dbc4138eb1329e3</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/opendata/testsExport.xlsx
+++ b/data/opendata/testsExport.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-17 10:57:55.917586</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1ffc7ca53484e83ec88d9a0903c481ed</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>- Erreur date- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/opendata/testsExport.xlsx
+++ b/data/opendata/testsExport.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +700,62 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-17 11:56:10.294401</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6bdfaff65fce99e1451c40021b394d42</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>- Erreur date- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-17 11:56:10.294401</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6bdfaff65fce99e1451c40021b394d42</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/opendata/testsExport.xlsx
+++ b/data/opendata/testsExport.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14 16:34:29.291064</t>
+          <t>2026-05-17 16:31:33.507958</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9ffe7f6c697cebe52d682105e6ee8751</t>
+          <t>2855e37ac952d181624675dbc0e2b9cd</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -473,286 +473,6 @@
         </is>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-14 16:34:29.291064</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>9ffe7f6c697cebe52d682105e6ee8751</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-14 16:34:29.291064</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>9ffe7f6c697cebe52d682105e6ee8751</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-16 14:22:46.435453</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>58ce0efd3aaa2a713dbc4138eb1329e3</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-16 16:43:44.479683</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>58ce0efd3aaa2a713dbc4138eb1329e3</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-16 17:00:45.411476</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>58ce0efd3aaa2a713dbc4138eb1329e3</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-16 17:01:56.145331</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>58ce0efd3aaa2a713dbc4138eb1329e3</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-05-16 17:03:07.071900</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>58ce0efd3aaa2a713dbc4138eb1329e3</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-05-17 10:57:55.917586</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1ffc7ca53484e83ec88d9a0903c481ed</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>- Erreur date- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-05-17 11:56:10.294401</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>6bdfaff65fce99e1451c40021b394d42</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>- Erreur date- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05-17 11:56:10.294401</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6bdfaff65fce99e1451c40021b394d42</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
-        </is>
-      </c>
-      <c r="F12" t="b">
         <v>0</v>
       </c>
     </row>
